--- a/Results/Phase 2/Hydrogen/hydrogen climate change breakdown results modified.xlsx
+++ b/Results/Phase 2/Hydrogen/hydrogen climate change breakdown results modified.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Ongoing projects\Prospective LCA\Results\Phase 2\Hydrogen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2208F35D-6748-4712-89B0-0CDACFF6A054}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BD2A499-131C-446D-BC3A-62AEA9C9B64E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="14025" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="14025" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="hydrogenBAU" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="55">
   <si>
     <t>name</t>
   </si>
@@ -168,15 +168,52 @@
   <si>
     <t>heat from natural gas</t>
   </si>
+  <si>
+    <r>
+      <t>m</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>3</t>
+    </r>
+  </si>
+  <si>
+    <t>Direct emissions</t>
+  </si>
+  <si>
+    <t>SMR</t>
+  </si>
+  <si>
+    <t>Case</t>
+  </si>
+  <si>
+    <t>Heat</t>
+  </si>
+  <si>
+    <t>Heat with CCS</t>
+  </si>
+  <si>
+    <t>SMR with CCS</t>
+  </si>
+  <si>
+    <t>Direct emissions modified</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="171" formatCode="0.000"/>
+    <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -188,6 +225,7 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -195,16 +233,36 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <vertAlign val="superscript"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -227,16 +285,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -244,6 +311,19 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2547,10 +2627,10 @@
         <v>1.7671355246452527</v>
       </c>
       <c r="Z2">
-        <v>0.29183908706271927</v>
+        <v>1.5529615759019688</v>
       </c>
       <c r="AA2">
-        <v>8.9251899806148032</v>
+        <v>7.6640674917755538</v>
       </c>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.25">
@@ -2630,10 +2710,10 @@
         <v>1.7444982837551939</v>
       </c>
       <c r="Z3">
-        <v>0.28810058957747414</v>
+        <v>1.5492230784167238</v>
       </c>
       <c r="AA3">
-        <v>8.9251899803844559</v>
+        <v>7.6640674915452065</v>
       </c>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.25">
@@ -2713,10 +2793,10 @@
         <v>1.7283797535670131</v>
       </c>
       <c r="Z4">
-        <v>0.28543864482603476</v>
+        <v>1.5465611336652842</v>
       </c>
       <c r="AA4">
-        <v>8.9251899802415835</v>
+        <v>7.6640674914023341</v>
       </c>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.25">
@@ -2796,10 +2876,10 @@
         <v>1.7193781165552748</v>
       </c>
       <c r="Z5">
-        <v>0.28395204151183617</v>
+        <v>1.5450745303510858</v>
       </c>
       <c r="AA5">
-        <v>8.9251899802234078</v>
+        <v>7.6640674913841584</v>
       </c>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.25">
@@ -2879,10 +2959,10 @@
         <v>1.6401879880999952</v>
       </c>
       <c r="Z6">
-        <v>0.2708739416884467</v>
+        <v>1.5319964305276963</v>
       </c>
       <c r="AA6">
-        <v>8.9251899796070955</v>
+        <v>7.6640674907678461</v>
       </c>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.25">
@@ -2962,10 +3042,10 @@
         <v>1.5900736332158676</v>
       </c>
       <c r="Z7">
-        <v>0.26259765083573644</v>
+        <v>1.523720139674986</v>
       </c>
       <c r="AA7">
-        <v>8.9251899791134104</v>
+        <v>7.664067490274161</v>
       </c>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.25">
@@ -3045,10 +3125,10 @@
         <v>1.5665382855794561</v>
       </c>
       <c r="Z8">
-        <v>0.25871083272126677</v>
+        <v>1.5198333215605164</v>
       </c>
       <c r="AA8">
-        <v>8.9251899788831945</v>
+        <v>7.6640674900439452</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.25">
@@ -3128,10 +3208,10 @@
         <v>1.7084465432361213</v>
       </c>
       <c r="Z9">
-        <v>0.28214671286944959</v>
+        <v>1.5432692017086991</v>
       </c>
       <c r="AA9">
-        <v>8.9251899800520338</v>
+        <v>7.6640674912127844</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.25">
@@ -3211,10 +3291,10 @@
         <v>1.6466558636492847</v>
       </c>
       <c r="Z10">
-        <v>0.27194209909302319</v>
+        <v>1.5330645879322728</v>
       </c>
       <c r="AA10">
-        <v>8.9251899795163201</v>
+        <v>7.6640674906770707</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
@@ -3294,10 +3374,10 @@
         <v>1.6179942126308127</v>
       </c>
       <c r="Z11">
-        <v>0.26720868167806838</v>
+        <v>1.5283311705173179</v>
       </c>
       <c r="AA11">
-        <v>8.9251899794676106</v>
+        <v>7.6640674906283612</v>
       </c>
     </row>
   </sheetData>
@@ -3479,10 +3559,10 @@
         <v>1.7394730210054847</v>
       </c>
       <c r="AB2">
-        <v>0.28727067694617225</v>
+        <v>0.41328841732184762</v>
       </c>
       <c r="AC2">
-        <v>2.6131052482117791</v>
+        <v>2.4870875078361037</v>
       </c>
     </row>
     <row r="3" spans="1:29" x14ac:dyDescent="0.25">
@@ -3568,10 +3648,10 @@
         <v>1.7171901404628815</v>
       </c>
       <c r="AB3">
-        <v>0.28359070140157644</v>
+        <v>0.40960844177725175</v>
       </c>
       <c r="AC3">
-        <v>2.6131052489612641</v>
+        <v>2.4870875085855886</v>
       </c>
     </row>
     <row r="4" spans="1:29" x14ac:dyDescent="0.25">
@@ -3657,10 +3737,10 @@
         <v>1.7013239275948924</v>
       </c>
       <c r="AB4">
-        <v>0.2809704263779807</v>
+        <v>0.40698816675365601</v>
       </c>
       <c r="AC4">
-        <v>2.6131052494752121</v>
+        <v>2.4870875090995366</v>
       </c>
     </row>
     <row r="5" spans="1:29" x14ac:dyDescent="0.25">
@@ -3746,10 +3826,10 @@
         <v>1.6924632010074727</v>
       </c>
       <c r="AB5">
-        <v>0.27950709415364328</v>
+        <v>0.40552483452931865</v>
       </c>
       <c r="AC5">
-        <v>2.6131052496112139</v>
+        <v>2.4870875092355385</v>
       </c>
     </row>
     <row r="6" spans="1:29" x14ac:dyDescent="0.25">
@@ -3835,10 +3915,10 @@
         <v>1.6145127042533678</v>
       </c>
       <c r="AB6">
-        <v>0.2666337171593291</v>
+        <v>0.39265145753500441</v>
       </c>
       <c r="AC6">
-        <v>2.613105250782779</v>
+        <v>2.4870875104071035</v>
       </c>
     </row>
     <row r="7" spans="1:29" x14ac:dyDescent="0.25">
@@ -3924,10 +4004,10 @@
         <v>1.5651828327917381</v>
       </c>
       <c r="AB7">
-        <v>0.25848698225897487</v>
+        <v>0.38450472263465019</v>
       </c>
       <c r="AC7">
-        <v>2.6131052522577689</v>
+        <v>2.4870875118820934</v>
       </c>
     </row>
     <row r="8" spans="1:29" x14ac:dyDescent="0.25">
@@ -4013,10 +4093,10 @@
         <v>1.5420159043459181</v>
       </c>
       <c r="AB8">
-        <v>0.25466100787648788</v>
+        <v>0.38067874825216319</v>
       </c>
       <c r="AC8">
-        <v>2.613105253077773</v>
+        <v>2.4870875127020975</v>
       </c>
     </row>
     <row r="9" spans="1:29" x14ac:dyDescent="0.25">
@@ -4102,10 +4182,10 @@
         <v>1.6817027490779966</v>
       </c>
       <c r="AB9">
-        <v>0.27773002588486345</v>
+        <v>0.40374776626053877</v>
       </c>
       <c r="AC9">
-        <v>2.6131052498379579</v>
+        <v>2.4870875094622824</v>
       </c>
     </row>
     <row r="10" spans="1:29" x14ac:dyDescent="0.25">
@@ -4191,10 +4271,10 @@
         <v>1.6208793325420912</v>
       </c>
       <c r="AB10">
-        <v>0.26768515377046381</v>
+        <v>0.39370289414613913</v>
       </c>
       <c r="AC10">
-        <v>2.613105250900198</v>
+        <v>2.4870875105245225</v>
       </c>
     </row>
     <row r="11" spans="1:29" x14ac:dyDescent="0.25">
@@ -4280,10 +4360,10 @@
         <v>1.592666347183135</v>
       </c>
       <c r="AB11">
-        <v>0.26302583263994406</v>
+        <v>0.38904357301561943</v>
       </c>
       <c r="AC11">
-        <v>2.6131052510311199</v>
+        <v>2.4870875106554444</v>
       </c>
     </row>
   </sheetData>
@@ -5209,7 +5289,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8AD273D-583A-4357-8767-B2CE3C4BA43A}">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
@@ -5218,9 +5298,16 @@
     <col min="4" max="4" width="11.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="24.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>42</v>
       </c>
@@ -5239,8 +5326,29 @@
       <c r="F1" s="3" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H1" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="L1" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="M1" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="N1" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="O1" s="9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>14.174001243299999</v>
       </c>
@@ -5259,8 +5367,33 @@
       <c r="F2" s="2">
         <v>1.7394730210054847</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H2" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="I2" s="2">
+        <v>2.8998114999999991E-2</v>
+      </c>
+      <c r="J2" s="2">
+        <v>5.904674911480768E-2</v>
+      </c>
+      <c r="L2" s="5">
+        <f>hydrogenBAUWOElec!Z2+heat!$J$3</f>
+        <v>2.8140840647412184</v>
+      </c>
+      <c r="M2" s="5">
+        <f>hydrogenBAUWOElec!AA2-heat!$J$3</f>
+        <v>6.4029450029363044</v>
+      </c>
+      <c r="N2" s="5">
+        <f>hydrogenBlueWOElec!AB2+heat!$J$5</f>
+        <v>0.53930615769752299</v>
+      </c>
+      <c r="O2" s="5">
+        <f>hydrogenBlueWOElec!AC2-heat!$J$5</f>
+        <v>2.3610697674604282</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>14.174001243299999</v>
       </c>
@@ -5279,8 +5412,35 @@
       <c r="F3" s="2">
         <v>1.7171901404628815</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H3" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="I3" s="2">
+        <f>4.36956877723609*A2/100</f>
+        <v>0.61934273281229191</v>
+      </c>
+      <c r="J3" s="2">
+        <f>I3*J2/I2</f>
+        <v>1.2611224888392496</v>
+      </c>
+      <c r="L3" s="5">
+        <f>hydrogenBAUWOElec!Z3+heat!$J$3</f>
+        <v>2.8103455672559736</v>
+      </c>
+      <c r="M3" s="5">
+        <f>hydrogenBAUWOElec!AA3-heat!$J$3</f>
+        <v>6.4029450027059571</v>
+      </c>
+      <c r="N3" s="5">
+        <f>hydrogenBlueWOElec!AB3+heat!$J$5</f>
+        <v>0.53562618215292712</v>
+      </c>
+      <c r="O3" s="5">
+        <f>hydrogenBlueWOElec!AC3-heat!$J$5</f>
+        <v>2.3610697682099131</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>14.174001243299999</v>
       </c>
@@ -5299,8 +5459,33 @@
       <c r="F4" s="2">
         <v>1.7013239275948924</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H4" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="I4" s="2">
+        <v>2.8998114999999991E-2</v>
+      </c>
+      <c r="J4" s="2">
+        <v>5.994080484482597E-3</v>
+      </c>
+      <c r="L4" s="5">
+        <f>hydrogenBAUWOElec!Z4+heat!$J$3</f>
+        <v>2.8076836225045341</v>
+      </c>
+      <c r="M4" s="5">
+        <f>hydrogenBAUWOElec!AA4-heat!$J$3</f>
+        <v>6.4029450025630847</v>
+      </c>
+      <c r="N4" s="5">
+        <f>hydrogenBlueWOElec!AB4+heat!$J$5</f>
+        <v>0.53300590712933138</v>
+      </c>
+      <c r="O4" s="5">
+        <f>hydrogenBlueWOElec!AC4-heat!$J$5</f>
+        <v>2.3610697687238611</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>14.174001243299999</v>
       </c>
@@ -5319,8 +5504,35 @@
       <c r="F5" s="2">
         <v>1.6924632010074727</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H5" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I5" s="7">
+        <f>4.30116813081211*D2/100</f>
+        <v>0.60964762433773179</v>
+      </c>
+      <c r="J5" s="2">
+        <f>I5*J4/I4</f>
+        <v>0.12601774037567534</v>
+      </c>
+      <c r="L5" s="5">
+        <f>hydrogenBAUWOElec!Z5+heat!$J$3</f>
+        <v>2.8061970191903356</v>
+      </c>
+      <c r="M5" s="5">
+        <f>hydrogenBAUWOElec!AA5-heat!$J$3</f>
+        <v>6.4029450025449091</v>
+      </c>
+      <c r="N5" s="5">
+        <f>hydrogenBlueWOElec!AB5+heat!$J$5</f>
+        <v>0.53154257490499401</v>
+      </c>
+      <c r="O5" s="5">
+        <f>hydrogenBlueWOElec!AC5-heat!$J$5</f>
+        <v>2.361069768859863</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>14.174001243299999</v>
       </c>
@@ -5339,8 +5551,24 @@
       <c r="F6" s="2">
         <v>1.6145127042533678</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="L6" s="5">
+        <f>hydrogenBAUWOElec!Z6+heat!$J$3</f>
+        <v>2.7931189193669459</v>
+      </c>
+      <c r="M6" s="5">
+        <f>hydrogenBAUWOElec!AA6-heat!$J$3</f>
+        <v>6.4029450019285967</v>
+      </c>
+      <c r="N6" s="5">
+        <f>hydrogenBlueWOElec!AB6+heat!$J$5</f>
+        <v>0.51866919791067978</v>
+      </c>
+      <c r="O6" s="5">
+        <f>hydrogenBlueWOElec!AC6-heat!$J$5</f>
+        <v>2.361069770031428</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>14.174001243299999</v>
       </c>
@@ -5359,8 +5587,24 @@
       <c r="F7" s="2">
         <v>1.5651828327917381</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="L7" s="5">
+        <f>hydrogenBAUWOElec!Z7+heat!$J$3</f>
+        <v>2.7848426285142356</v>
+      </c>
+      <c r="M7" s="5">
+        <f>hydrogenBAUWOElec!AA7-heat!$J$3</f>
+        <v>6.4029450014349116</v>
+      </c>
+      <c r="N7" s="5">
+        <f>hydrogenBlueWOElec!AB7+heat!$J$5</f>
+        <v>0.51052246301032556</v>
+      </c>
+      <c r="O7" s="5">
+        <f>hydrogenBlueWOElec!AC7-heat!$J$5</f>
+        <v>2.3610697715064179</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>14.174001243299999</v>
       </c>
@@ -5379,8 +5623,24 @@
       <c r="F8" s="2">
         <v>1.5420159043459181</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="L8" s="5">
+        <f>hydrogenBAUWOElec!Z8+heat!$J$3</f>
+        <v>2.780955810399766</v>
+      </c>
+      <c r="M8" s="5">
+        <f>hydrogenBAUWOElec!AA8-heat!$J$3</f>
+        <v>6.4029450012046958</v>
+      </c>
+      <c r="N8" s="5">
+        <f>hydrogenBlueWOElec!AB8+heat!$J$5</f>
+        <v>0.50669648862783856</v>
+      </c>
+      <c r="O8" s="5">
+        <f>hydrogenBlueWOElec!AC8-heat!$J$5</f>
+        <v>2.361069772326422</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>14.174001243299999</v>
       </c>
@@ -5399,8 +5659,24 @@
       <c r="F9" s="2">
         <v>1.6817027490779966</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="L9" s="5">
+        <f>hydrogenBAUWOElec!Z9+heat!$J$3</f>
+        <v>2.8043916905479485</v>
+      </c>
+      <c r="M9" s="5">
+        <f>hydrogenBAUWOElec!AA9-heat!$J$3</f>
+        <v>6.402945002373535</v>
+      </c>
+      <c r="N9" s="5">
+        <f>hydrogenBlueWOElec!AB9+heat!$J$5</f>
+        <v>0.52976550663621413</v>
+      </c>
+      <c r="O9" s="5">
+        <f>hydrogenBlueWOElec!AC9-heat!$J$5</f>
+        <v>2.3610697690866069</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>14.174001243299999</v>
       </c>
@@ -5419,8 +5695,24 @@
       <c r="F10" s="2">
         <v>1.6208793325420912</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="L10" s="5">
+        <f>hydrogenBAUWOElec!Z10+heat!$J$3</f>
+        <v>2.7941870767715224</v>
+      </c>
+      <c r="M10" s="5">
+        <f>hydrogenBAUWOElec!AA10-heat!$J$3</f>
+        <v>6.4029450018378213</v>
+      </c>
+      <c r="N10" s="5">
+        <f>hydrogenBlueWOElec!AB10+heat!$J$5</f>
+        <v>0.5197206345218145</v>
+      </c>
+      <c r="O10" s="5">
+        <f>hydrogenBlueWOElec!AC10-heat!$J$5</f>
+        <v>2.361069770148847</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>14.174001243299999</v>
       </c>
@@ -5439,6 +5731,34 @@
       <c r="F11" s="2">
         <v>1.592666347183135</v>
       </c>
+      <c r="L11" s="5">
+        <f>hydrogenBAUWOElec!Z11+heat!$J$3</f>
+        <v>2.7894536593565675</v>
+      </c>
+      <c r="M11" s="5">
+        <f>hydrogenBAUWOElec!AA11-heat!$J$3</f>
+        <v>6.4029450017891119</v>
+      </c>
+      <c r="N11" s="5">
+        <f>hydrogenBlueWOElec!AB11+heat!$J$5</f>
+        <v>0.51506131339129479</v>
+      </c>
+      <c r="O11" s="5">
+        <f>hydrogenBlueWOElec!AC11-heat!$J$5</f>
+        <v>2.3610697702797689</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="L12" s="6"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="L13" s="6"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="L14" s="6"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="L15" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Results/Phase 2/Hydrogen/hydrogen climate change breakdown results modified.xlsx
+++ b/Results/Phase 2/Hydrogen/hydrogen climate change breakdown results modified.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Ongoing projects\Prospective LCA\Results\Phase 2\Hydrogen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BD2A499-131C-446D-BC3A-62AEA9C9B64E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98A76F01-0D59-4A18-ACCC-8604C9454159}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="14025" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="14025" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="hydrogenBAU" sheetId="1" r:id="rId1"/>
@@ -5377,20 +5377,16 @@
         <v>5.904674911480768E-2</v>
       </c>
       <c r="L2" s="5">
-        <f>hydrogenBAUWOElec!Z2+heat!$J$3</f>
-        <v>2.8140840647412184</v>
+        <v>1.5529615759019688</v>
       </c>
       <c r="M2" s="5">
-        <f>hydrogenBAUWOElec!AA2-heat!$J$3</f>
-        <v>6.4029450029363044</v>
+        <v>7.6640674917755538</v>
       </c>
       <c r="N2" s="5">
-        <f>hydrogenBlueWOElec!AB2+heat!$J$5</f>
-        <v>0.53930615769752299</v>
+        <v>0.41328841732184762</v>
       </c>
       <c r="O2" s="5">
-        <f>hydrogenBlueWOElec!AC2-heat!$J$5</f>
-        <v>2.3610697674604282</v>
+        <v>2.4870875078361037</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="17.25" x14ac:dyDescent="0.25">
@@ -5424,20 +5420,16 @@
         <v>1.2611224888392496</v>
       </c>
       <c r="L3" s="5">
-        <f>hydrogenBAUWOElec!Z3+heat!$J$3</f>
-        <v>2.8103455672559736</v>
+        <v>1.5492230784167238</v>
       </c>
       <c r="M3" s="5">
-        <f>hydrogenBAUWOElec!AA3-heat!$J$3</f>
-        <v>6.4029450027059571</v>
+        <v>7.6640674915452065</v>
       </c>
       <c r="N3" s="5">
-        <f>hydrogenBlueWOElec!AB3+heat!$J$5</f>
-        <v>0.53562618215292712</v>
+        <v>0.40960844177725175</v>
       </c>
       <c r="O3" s="5">
-        <f>hydrogenBlueWOElec!AC3-heat!$J$5</f>
-        <v>2.3610697682099131</v>
+        <v>2.4870875085855886</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
@@ -5469,20 +5461,16 @@
         <v>5.994080484482597E-3</v>
       </c>
       <c r="L4" s="5">
-        <f>hydrogenBAUWOElec!Z4+heat!$J$3</f>
-        <v>2.8076836225045341</v>
+        <v>1.5465611336652842</v>
       </c>
       <c r="M4" s="5">
-        <f>hydrogenBAUWOElec!AA4-heat!$J$3</f>
-        <v>6.4029450025630847</v>
+        <v>7.6640674914023341</v>
       </c>
       <c r="N4" s="5">
-        <f>hydrogenBlueWOElec!AB4+heat!$J$5</f>
-        <v>0.53300590712933138</v>
+        <v>0.40698816675365601</v>
       </c>
       <c r="O4" s="5">
-        <f>hydrogenBlueWOElec!AC4-heat!$J$5</f>
-        <v>2.3610697687238611</v>
+        <v>2.4870875090995366</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
@@ -5516,20 +5504,16 @@
         <v>0.12601774037567534</v>
       </c>
       <c r="L5" s="5">
-        <f>hydrogenBAUWOElec!Z5+heat!$J$3</f>
-        <v>2.8061970191903356</v>
+        <v>1.5450745303510858</v>
       </c>
       <c r="M5" s="5">
-        <f>hydrogenBAUWOElec!AA5-heat!$J$3</f>
-        <v>6.4029450025449091</v>
+        <v>7.6640674913841584</v>
       </c>
       <c r="N5" s="5">
-        <f>hydrogenBlueWOElec!AB5+heat!$J$5</f>
-        <v>0.53154257490499401</v>
+        <v>0.40552483452931865</v>
       </c>
       <c r="O5" s="5">
-        <f>hydrogenBlueWOElec!AC5-heat!$J$5</f>
-        <v>2.361069768859863</v>
+        <v>2.4870875092355385</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
@@ -5552,20 +5536,16 @@
         <v>1.6145127042533678</v>
       </c>
       <c r="L6" s="5">
-        <f>hydrogenBAUWOElec!Z6+heat!$J$3</f>
-        <v>2.7931189193669459</v>
+        <v>1.5319964305276963</v>
       </c>
       <c r="M6" s="5">
-        <f>hydrogenBAUWOElec!AA6-heat!$J$3</f>
-        <v>6.4029450019285967</v>
+        <v>7.6640674907678461</v>
       </c>
       <c r="N6" s="5">
-        <f>hydrogenBlueWOElec!AB6+heat!$J$5</f>
-        <v>0.51866919791067978</v>
+        <v>0.39265145753500441</v>
       </c>
       <c r="O6" s="5">
-        <f>hydrogenBlueWOElec!AC6-heat!$J$5</f>
-        <v>2.361069770031428</v>
+        <v>2.4870875104071035</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
@@ -5588,20 +5568,16 @@
         <v>1.5651828327917381</v>
       </c>
       <c r="L7" s="5">
-        <f>hydrogenBAUWOElec!Z7+heat!$J$3</f>
-        <v>2.7848426285142356</v>
+        <v>1.523720139674986</v>
       </c>
       <c r="M7" s="5">
-        <f>hydrogenBAUWOElec!AA7-heat!$J$3</f>
-        <v>6.4029450014349116</v>
+        <v>7.664067490274161</v>
       </c>
       <c r="N7" s="5">
-        <f>hydrogenBlueWOElec!AB7+heat!$J$5</f>
-        <v>0.51052246301032556</v>
+        <v>0.38450472263465019</v>
       </c>
       <c r="O7" s="5">
-        <f>hydrogenBlueWOElec!AC7-heat!$J$5</f>
-        <v>2.3610697715064179</v>
+        <v>2.4870875118820934</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
@@ -5624,20 +5600,16 @@
         <v>1.5420159043459181</v>
       </c>
       <c r="L8" s="5">
-        <f>hydrogenBAUWOElec!Z8+heat!$J$3</f>
-        <v>2.780955810399766</v>
+        <v>1.5198333215605164</v>
       </c>
       <c r="M8" s="5">
-        <f>hydrogenBAUWOElec!AA8-heat!$J$3</f>
-        <v>6.4029450012046958</v>
+        <v>7.6640674900439452</v>
       </c>
       <c r="N8" s="5">
-        <f>hydrogenBlueWOElec!AB8+heat!$J$5</f>
-        <v>0.50669648862783856</v>
+        <v>0.38067874825216319</v>
       </c>
       <c r="O8" s="5">
-        <f>hydrogenBlueWOElec!AC8-heat!$J$5</f>
-        <v>2.361069772326422</v>
+        <v>2.4870875127020975</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
@@ -5660,20 +5632,16 @@
         <v>1.6817027490779966</v>
       </c>
       <c r="L9" s="5">
-        <f>hydrogenBAUWOElec!Z9+heat!$J$3</f>
-        <v>2.8043916905479485</v>
+        <v>1.5432692017086991</v>
       </c>
       <c r="M9" s="5">
-        <f>hydrogenBAUWOElec!AA9-heat!$J$3</f>
-        <v>6.402945002373535</v>
+        <v>7.6640674912127844</v>
       </c>
       <c r="N9" s="5">
-        <f>hydrogenBlueWOElec!AB9+heat!$J$5</f>
-        <v>0.52976550663621413</v>
+        <v>0.40374776626053877</v>
       </c>
       <c r="O9" s="5">
-        <f>hydrogenBlueWOElec!AC9-heat!$J$5</f>
-        <v>2.3610697690866069</v>
+        <v>2.4870875094622824</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
@@ -5696,20 +5664,16 @@
         <v>1.6208793325420912</v>
       </c>
       <c r="L10" s="5">
-        <f>hydrogenBAUWOElec!Z10+heat!$J$3</f>
-        <v>2.7941870767715224</v>
+        <v>1.5330645879322728</v>
       </c>
       <c r="M10" s="5">
-        <f>hydrogenBAUWOElec!AA10-heat!$J$3</f>
-        <v>6.4029450018378213</v>
+        <v>7.6640674906770707</v>
       </c>
       <c r="N10" s="5">
-        <f>hydrogenBlueWOElec!AB10+heat!$J$5</f>
-        <v>0.5197206345218145</v>
+        <v>0.39370289414613913</v>
       </c>
       <c r="O10" s="5">
-        <f>hydrogenBlueWOElec!AC10-heat!$J$5</f>
-        <v>2.361069770148847</v>
+        <v>2.4870875105245225</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
@@ -5732,20 +5696,16 @@
         <v>1.592666347183135</v>
       </c>
       <c r="L11" s="5">
-        <f>hydrogenBAUWOElec!Z11+heat!$J$3</f>
-        <v>2.7894536593565675</v>
+        <v>1.5283311705173179</v>
       </c>
       <c r="M11" s="5">
-        <f>hydrogenBAUWOElec!AA11-heat!$J$3</f>
-        <v>6.4029450017891119</v>
+        <v>7.6640674906283612</v>
       </c>
       <c r="N11" s="5">
-        <f>hydrogenBlueWOElec!AB11+heat!$J$5</f>
-        <v>0.51506131339129479</v>
+        <v>0.38904357301561943</v>
       </c>
       <c r="O11" s="5">
-        <f>hydrogenBlueWOElec!AC11-heat!$J$5</f>
-        <v>2.3610697702797689</v>
+        <v>2.4870875106554444</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">

--- a/Results/Phase 2/Hydrogen/hydrogen climate change breakdown results modified.xlsx
+++ b/Results/Phase 2/Hydrogen/hydrogen climate change breakdown results modified.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20404"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20405"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Ongoing projects\Prospective LCA\Results\Phase 2\Hydrogen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98A76F01-0D59-4A18-ACCC-8604C9454159}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3CC0039-C750-47EB-ACC3-4CEA3D0CC46E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="14025" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="14025" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="hydrogenBAU" sheetId="1" r:id="rId1"/>
@@ -213,7 +213,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -235,6 +235,14 @@
     </font>
     <font>
       <vertAlign val="superscript"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -298,7 +306,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -323,6 +331,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -627,7 +638,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z11"/>
+  <dimension ref="A1:Z22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:26" x14ac:dyDescent="0.25">
@@ -1505,6 +1516,66 @@
       </c>
       <c r="Z11">
         <v>8.9251899774749894</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="D13" s="5">
+        <f>($D$2-D3)/$D$2*100</f>
+        <v>1.7381816828182749E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="D14" s="5">
+        <f t="shared" ref="D14:D21" si="0">($D$2-D4)/$D$2*100</f>
+        <v>-0.18536699616302277</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="D15" s="5">
+        <f t="shared" si="0"/>
+        <v>-0.75119689889022923</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="D16" s="5">
+        <f t="shared" si="0"/>
+        <v>-4.1722557989019737</v>
+      </c>
+    </row>
+    <row r="17" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D17" s="5">
+        <f t="shared" si="0"/>
+        <v>-5.0159405042811356</v>
+      </c>
+    </row>
+    <row r="18" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D18" s="5">
+        <f t="shared" si="0"/>
+        <v>-5.1242939129246494</v>
+      </c>
+    </row>
+    <row r="19" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D19" s="5">
+        <f t="shared" si="0"/>
+        <v>-0.97102431619190166</v>
+      </c>
+    </row>
+    <row r="20" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D20" s="5">
+        <f t="shared" si="0"/>
+        <v>-3.7542312601776713</v>
+      </c>
+    </row>
+    <row r="21" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D21" s="5">
+        <f t="shared" si="0"/>
+        <v>-5.5531358956240853</v>
+      </c>
+    </row>
+    <row r="22" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D22" s="5">
+        <f>MAX(D13:D21)</f>
+        <v>1.7381816828182749E-2</v>
       </c>
     </row>
   </sheetData>
@@ -2467,7 +2538,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:AA11"/>
+  <dimension ref="A1:AA22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:27" x14ac:dyDescent="0.25">
@@ -3378,6 +3449,66 @@
       </c>
       <c r="AA11">
         <v>7.6640674906283612</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="D13" s="5">
+        <f>($D$2-D3)/$D$2*100</f>
+        <v>0.29711373958273335</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="D14" s="5">
+        <f t="shared" ref="D14:D21" si="0">($D$2-D4)/$D$2*100</f>
+        <v>0.48442694640235984</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="D15" s="5">
+        <f t="shared" si="0"/>
+        <v>0.57867213506391268</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="D16" s="5">
+        <f t="shared" si="0"/>
+        <v>1.6852932702094574</v>
+      </c>
+    </row>
+    <row r="17" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D17" s="5">
+        <f t="shared" si="0"/>
+        <v>2.2930191812655667</v>
+      </c>
+    </row>
+    <row r="18" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D18" s="5">
+        <f t="shared" si="0"/>
+        <v>2.567283455580033</v>
+      </c>
+    </row>
+    <row r="19" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D19" s="5">
+        <f t="shared" si="0"/>
+        <v>0.75083893124895196</v>
+      </c>
+    </row>
+    <row r="20" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D20" s="5">
+        <f t="shared" si="0"/>
+        <v>1.5478684584066795</v>
+      </c>
+    </row>
+    <row r="21" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D21" s="5">
+        <f t="shared" si="0"/>
+        <v>1.9655946023177087</v>
+      </c>
+    </row>
+    <row r="22" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D22" s="10">
+        <f>MAX(D13:D21)</f>
+        <v>2.567283455580033</v>
       </c>
     </row>
   </sheetData>
@@ -4373,7 +4504,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -4822,6 +4953,66 @@
       </c>
       <c r="M11">
         <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="D13" s="5">
+        <f>(hydrogenBAUWOElec!$D$2-D3)/hydrogenBAUWOElec!$D$2*100</f>
+        <v>80.577939721373113</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="D14" s="5">
+        <f>(hydrogenBAUWOElec!$D$2-D4)/hydrogenBAUWOElec!$D$2*100</f>
+        <v>82.485094021171363</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="D15" s="5">
+        <f>(hydrogenBAUWOElec!$D$2-D5)/hydrogenBAUWOElec!$D$2*100</f>
+        <v>82.877741856043713</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="D16" s="5">
+        <f>(hydrogenBAUWOElec!$D$2-D6)/hydrogenBAUWOElec!$D$2*100</f>
+        <v>86.116410346263422</v>
+      </c>
+    </row>
+    <row r="17" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D17" s="5">
+        <f>(hydrogenBAUWOElec!$D$2-D7)/hydrogenBAUWOElec!$D$2*100</f>
+        <v>88.853461852085417</v>
+      </c>
+    </row>
+    <row r="18" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D18" s="5">
+        <f>(hydrogenBAUWOElec!$D$2-D8)/hydrogenBAUWOElec!$D$2*100</f>
+        <v>89.584076216398984</v>
+      </c>
+    </row>
+    <row r="19" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D19" s="5">
+        <f>(hydrogenBAUWOElec!$D$2-D9)/hydrogenBAUWOElec!$D$2*100</f>
+        <v>82.326776187527429</v>
+      </c>
+    </row>
+    <row r="20" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D20" s="5">
+        <f>(hydrogenBAUWOElec!$D$2-D10)/hydrogenBAUWOElec!$D$2*100</f>
+        <v>86.271918078178857</v>
+      </c>
+    </row>
+    <row r="21" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D21" s="5">
+        <f>(hydrogenBAUWOElec!$D$2-D11)/hydrogenBAUWOElec!$D$2*100</f>
+        <v>88.06566388704266</v>
+      </c>
+    </row>
+    <row r="22" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D22" s="10">
+        <f>MAX(D13:D21)</f>
+        <v>89.584076216398984</v>
       </c>
     </row>
   </sheetData>
@@ -4831,7 +5022,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -5280,6 +5471,66 @@
       </c>
       <c r="M11">
         <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="D13" s="5">
+        <f>(hydrogenBAUWOElec!$D$2-D3)/hydrogenBAUWOElec!$D$2*100</f>
+        <v>69.67503239956892</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="D14" s="5">
+        <f>(hydrogenBAUWOElec!$D$2-D4)/hydrogenBAUWOElec!$D$2*100</f>
+        <v>73.637129037910597</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="D15" s="5">
+        <f>(hydrogenBAUWOElec!$D$2-D5)/hydrogenBAUWOElec!$D$2*100</f>
+        <v>75.281367486677297</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="D16" s="5">
+        <f>(hydrogenBAUWOElec!$D$2-D6)/hydrogenBAUWOElec!$D$2*100</f>
+        <v>79.28573758113005</v>
+      </c>
+    </row>
+    <row r="17" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D17" s="5">
+        <f>(hydrogenBAUWOElec!$D$2-D7)/hydrogenBAUWOElec!$D$2*100</f>
+        <v>83.433626300651454</v>
+      </c>
+    </row>
+    <row r="18" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D18" s="5">
+        <f>(hydrogenBAUWOElec!$D$2-D8)/hydrogenBAUWOElec!$D$2*100</f>
+        <v>84.859643916465004</v>
+      </c>
+    </row>
+    <row r="19" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D19" s="5">
+        <f>(hydrogenBAUWOElec!$D$2-D9)/hydrogenBAUWOElec!$D$2*100</f>
+        <v>71.869351839805077</v>
+      </c>
+    </row>
+    <row r="20" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D20" s="5">
+        <f>(hydrogenBAUWOElec!$D$2-D10)/hydrogenBAUWOElec!$D$2*100</f>
+        <v>78.523131820021092</v>
+      </c>
+    </row>
+    <row r="21" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D21" s="5">
+        <f>(hydrogenBAUWOElec!$D$2-D11)/hydrogenBAUWOElec!$D$2*100</f>
+        <v>83.299915621241055</v>
+      </c>
+    </row>
+    <row r="22" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D22" s="10">
+        <f>MAX(D13:D21)</f>
+        <v>84.859643916465004</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Phase 2/Hydrogen/hydrogen climate change breakdown results modified.xlsx
+++ b/Results/Phase 2/Hydrogen/hydrogen climate change breakdown results modified.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20405"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11210"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Ongoing projects\Prospective LCA\Results\Phase 2\Hydrogen\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/abhinabera/Desktop/Prospective-LCA/Results/Phase 2/Hydrogen/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3CC0039-C750-47EB-ACC3-4CEA3D0CC46E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4024E4D7-682A-EF4C-A252-C73B108EFF95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="14025" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="14020" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="hydrogenBAU" sheetId="1" r:id="rId1"/>
@@ -22,6 +22,19 @@
     <sheet name="heat" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -306,7 +319,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -324,9 +337,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -639,9 +649,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Z22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -718,7 +728,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -798,7 +808,7 @@
         <v>8.925189945964096</v>
       </c>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -878,7 +888,7 @@
         <v>8.9251899470263911</v>
       </c>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -958,7 +968,7 @@
         <v>8.9251899486073523</v>
       </c>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -1038,7 +1048,7 @@
         <v>8.92518995142912</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -1118,7 +1128,7 @@
         <v>8.9251899704523812</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -1198,7 +1208,7 @@
         <v>8.9251899763420965</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -1278,7 +1288,7 @@
         <v>8.9251899778341794</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -1358,7 +1368,7 @@
         <v>8.9251899529845442</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -1438,7 +1448,7 @@
         <v>8.9251899679516775</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -1518,61 +1528,61 @@
         <v>8.9251899774749894</v>
       </c>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D13" s="5">
         <f>($D$2-D3)/$D$2*100</f>
         <v>1.7381816828182749E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D14" s="5">
         <f t="shared" ref="D14:D21" si="0">($D$2-D4)/$D$2*100</f>
         <v>-0.18536699616302277</v>
       </c>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D15" s="5">
         <f t="shared" si="0"/>
         <v>-0.75119689889022923</v>
       </c>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="5">
         <f t="shared" si="0"/>
         <v>-4.1722557989019737</v>
       </c>
     </row>
-    <row r="17" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D17" s="5">
         <f t="shared" si="0"/>
         <v>-5.0159405042811356</v>
       </c>
     </row>
-    <row r="18" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D18" s="5">
         <f t="shared" si="0"/>
         <v>-5.1242939129246494</v>
       </c>
     </row>
-    <row r="19" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D19" s="5">
         <f t="shared" si="0"/>
         <v>-0.97102431619190166</v>
       </c>
     </row>
-    <row r="20" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D20" s="5">
         <f t="shared" si="0"/>
         <v>-3.7542312601776713</v>
       </c>
     </row>
-    <row r="21" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D21" s="5">
         <f t="shared" si="0"/>
         <v>-5.5531358956240853</v>
       </c>
     </row>
-    <row r="22" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D22" s="5">
         <f>MAX(D13:D21)</f>
         <v>1.7381816828182749E-2</v>
@@ -1586,9 +1596,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AB11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1671,7 +1681,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -1757,7 +1767,7 @@
         <v>2.6131052507600758</v>
       </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -1843,7 +1853,7 @@
         <v>2.6131052514145008</v>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -1929,7 +1939,7 @@
         <v>2.613105251801672</v>
       </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -2015,7 +2025,7 @@
         <v>2.6131052517288169</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -2101,7 +2111,7 @@
         <v>2.61310525145604</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -2187,7 +2197,7 @@
         <v>2.6131052524615779</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -2273,7 +2283,7 @@
         <v>2.6131052531549179</v>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -2359,7 +2369,7 @@
         <v>2.6131052518285678</v>
       </c>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -2445,7 +2455,7 @@
         <v>2.6131052517506932</v>
       </c>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -2539,9 +2549,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:AA22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2621,7 +2631,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -2704,7 +2714,7 @@
         <v>7.6640674917755538</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -2787,7 +2797,7 @@
         <v>7.6640674915452065</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -2870,7 +2880,7 @@
         <v>7.6640674914023341</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -2953,7 +2963,7 @@
         <v>7.6640674913841584</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -3036,7 +3046,7 @@
         <v>7.6640674907678461</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -3119,7 +3129,7 @@
         <v>7.664067490274161</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -3202,7 +3212,7 @@
         <v>7.6640674900439452</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -3285,7 +3295,7 @@
         <v>7.6640674912127844</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -3368,7 +3378,7 @@
         <v>7.6640674906770707</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -3451,65 +3461,35 @@
         <v>7.6640674906283612</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="D13" s="5">
-        <f>($D$2-D3)/$D$2*100</f>
-        <v>0.29711373958273335</v>
-      </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="D14" s="5">
-        <f t="shared" ref="D14:D21" si="0">($D$2-D4)/$D$2*100</f>
-        <v>0.48442694640235984</v>
-      </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="D15" s="5">
-        <f t="shared" si="0"/>
-        <v>0.57867213506391268</v>
-      </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="D16" s="5">
-        <f t="shared" si="0"/>
-        <v>1.6852932702094574</v>
-      </c>
-    </row>
-    <row r="17" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D17" s="5">
-        <f t="shared" si="0"/>
-        <v>2.2930191812655667</v>
-      </c>
-    </row>
-    <row r="18" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D18" s="5">
-        <f t="shared" si="0"/>
-        <v>2.567283455580033</v>
-      </c>
-    </row>
-    <row r="19" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D19" s="5">
-        <f t="shared" si="0"/>
-        <v>0.75083893124895196</v>
-      </c>
-    </row>
-    <row r="20" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D20" s="5">
-        <f t="shared" si="0"/>
-        <v>1.5478684584066795</v>
-      </c>
-    </row>
-    <row r="21" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D21" s="5">
-        <f t="shared" si="0"/>
-        <v>1.9655946023177087</v>
-      </c>
-    </row>
-    <row r="22" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D22" s="10">
-        <f>MAX(D13:D21)</f>
-        <v>2.567283455580033</v>
-      </c>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="D13" s="5"/>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="D14" s="5"/>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="D15" s="5"/>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="D16" s="5"/>
+    </row>
+    <row r="17" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D17" s="5"/>
+    </row>
+    <row r="18" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D18" s="5"/>
+    </row>
+    <row r="19" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D19" s="5"/>
+    </row>
+    <row r="20" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D21" s="5"/>
+    </row>
+    <row r="22" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D22" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3519,9 +3499,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:AC11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3607,7 +3587,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -3696,7 +3676,7 @@
         <v>2.4870875078361037</v>
       </c>
     </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -3785,7 +3765,7 @@
         <v>2.4870875085855886</v>
       </c>
     </row>
-    <row r="4" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -3874,7 +3854,7 @@
         <v>2.4870875090995366</v>
       </c>
     </row>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -3963,7 +3943,7 @@
         <v>2.4870875092355385</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -4052,7 +4032,7 @@
         <v>2.4870875104071035</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -4141,7 +4121,7 @@
         <v>2.4870875118820934</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -4230,7 +4210,7 @@
         <v>2.4870875127020975</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -4319,7 +4299,7 @@
         <v>2.4870875094622824</v>
       </c>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -4408,7 +4388,7 @@
         <v>2.4870875105245225</v>
       </c>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -4505,9 +4485,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:M22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4545,7 +4525,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -4586,7 +4566,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -4627,7 +4607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -4668,7 +4648,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -4709,7 +4689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -4750,7 +4730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -4791,7 +4771,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -4832,7 +4812,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -4873,7 +4853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -4914,7 +4894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -4955,65 +4935,35 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="D13" s="5">
-        <f>(hydrogenBAUWOElec!$D$2-D3)/hydrogenBAUWOElec!$D$2*100</f>
-        <v>80.577939721373113</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="D14" s="5">
-        <f>(hydrogenBAUWOElec!$D$2-D4)/hydrogenBAUWOElec!$D$2*100</f>
-        <v>82.485094021171363</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="D15" s="5">
-        <f>(hydrogenBAUWOElec!$D$2-D5)/hydrogenBAUWOElec!$D$2*100</f>
-        <v>82.877741856043713</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="D16" s="5">
-        <f>(hydrogenBAUWOElec!$D$2-D6)/hydrogenBAUWOElec!$D$2*100</f>
-        <v>86.116410346263422</v>
-      </c>
-    </row>
-    <row r="17" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D17" s="5">
-        <f>(hydrogenBAUWOElec!$D$2-D7)/hydrogenBAUWOElec!$D$2*100</f>
-        <v>88.853461852085417</v>
-      </c>
-    </row>
-    <row r="18" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D18" s="5">
-        <f>(hydrogenBAUWOElec!$D$2-D8)/hydrogenBAUWOElec!$D$2*100</f>
-        <v>89.584076216398984</v>
-      </c>
-    </row>
-    <row r="19" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D19" s="5">
-        <f>(hydrogenBAUWOElec!$D$2-D9)/hydrogenBAUWOElec!$D$2*100</f>
-        <v>82.326776187527429</v>
-      </c>
-    </row>
-    <row r="20" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D20" s="5">
-        <f>(hydrogenBAUWOElec!$D$2-D10)/hydrogenBAUWOElec!$D$2*100</f>
-        <v>86.271918078178857</v>
-      </c>
-    </row>
-    <row r="21" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D21" s="5">
-        <f>(hydrogenBAUWOElec!$D$2-D11)/hydrogenBAUWOElec!$D$2*100</f>
-        <v>88.06566388704266</v>
-      </c>
-    </row>
-    <row r="22" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D22" s="10">
-        <f>MAX(D13:D21)</f>
-        <v>89.584076216398984</v>
-      </c>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="D13" s="5"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="D14" s="5"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="D15" s="5"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="D16" s="5"/>
+    </row>
+    <row r="17" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D17" s="5"/>
+    </row>
+    <row r="18" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D18" s="5"/>
+    </row>
+    <row r="19" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D19" s="5"/>
+    </row>
+    <row r="20" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D21" s="5"/>
+    </row>
+    <row r="22" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D22" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5023,9 +4973,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:M22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5063,7 +5013,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -5104,7 +5054,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -5145,7 +5095,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -5186,7 +5136,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -5227,7 +5177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -5268,7 +5218,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -5309,7 +5259,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -5350,7 +5300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -5391,7 +5341,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -5432,7 +5382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -5473,65 +5423,35 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="D13" s="5">
-        <f>(hydrogenBAUWOElec!$D$2-D3)/hydrogenBAUWOElec!$D$2*100</f>
-        <v>69.67503239956892</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="D14" s="5">
-        <f>(hydrogenBAUWOElec!$D$2-D4)/hydrogenBAUWOElec!$D$2*100</f>
-        <v>73.637129037910597</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="D15" s="5">
-        <f>(hydrogenBAUWOElec!$D$2-D5)/hydrogenBAUWOElec!$D$2*100</f>
-        <v>75.281367486677297</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="D16" s="5">
-        <f>(hydrogenBAUWOElec!$D$2-D6)/hydrogenBAUWOElec!$D$2*100</f>
-        <v>79.28573758113005</v>
-      </c>
-    </row>
-    <row r="17" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D17" s="5">
-        <f>(hydrogenBAUWOElec!$D$2-D7)/hydrogenBAUWOElec!$D$2*100</f>
-        <v>83.433626300651454</v>
-      </c>
-    </row>
-    <row r="18" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D18" s="5">
-        <f>(hydrogenBAUWOElec!$D$2-D8)/hydrogenBAUWOElec!$D$2*100</f>
-        <v>84.859643916465004</v>
-      </c>
-    </row>
-    <row r="19" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D19" s="5">
-        <f>(hydrogenBAUWOElec!$D$2-D9)/hydrogenBAUWOElec!$D$2*100</f>
-        <v>71.869351839805077</v>
-      </c>
-    </row>
-    <row r="20" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D20" s="5">
-        <f>(hydrogenBAUWOElec!$D$2-D10)/hydrogenBAUWOElec!$D$2*100</f>
-        <v>78.523131820021092</v>
-      </c>
-    </row>
-    <row r="21" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D21" s="5">
-        <f>(hydrogenBAUWOElec!$D$2-D11)/hydrogenBAUWOElec!$D$2*100</f>
-        <v>83.299915621241055</v>
-      </c>
-    </row>
-    <row r="22" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D22" s="10">
-        <f>MAX(D13:D21)</f>
-        <v>84.859643916465004</v>
-      </c>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="D13" s="5"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="D14" s="5"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="D15" s="5"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="D16" s="5"/>
+    </row>
+    <row r="17" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D17" s="5"/>
+    </row>
+    <row r="18" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D18" s="5"/>
+    </row>
+    <row r="19" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D19" s="5"/>
+    </row>
+    <row r="20" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D21" s="5"/>
+    </row>
+    <row r="22" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D22" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5541,24 +5461,24 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8AD273D-583A-4357-8767-B2CE3C4BA43A}">
   <dimension ref="A1:O15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.5" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="24.5703125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="24.5" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="24.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>42</v>
       </c>
@@ -5586,20 +5506,20 @@
       <c r="J1" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="L1" s="8" t="s">
+      <c r="L1" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="M1" s="8" t="s">
+      <c r="M1" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="N1" s="9" t="s">
+      <c r="N1" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="O1" s="9" t="s">
+      <c r="O1" s="8" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
         <v>14.174001243299999</v>
       </c>
@@ -5640,7 +5560,7 @@
         <v>2.4870875078361037</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
         <v>14.174001243299999</v>
       </c>
@@ -5683,7 +5603,7 @@
         <v>2.4870875085855886</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>14.174001243299999</v>
       </c>
@@ -5724,7 +5644,7 @@
         <v>2.4870875090995366</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <v>14.174001243299999</v>
       </c>
@@ -5746,7 +5666,7 @@
       <c r="H5" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="I5" s="7">
+      <c r="I5" s="2">
         <f>4.30116813081211*D2/100</f>
         <v>0.60964762433773179</v>
       </c>
@@ -5767,7 +5687,7 @@
         <v>2.4870875092355385</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <v>14.174001243299999</v>
       </c>
@@ -5799,7 +5719,7 @@
         <v>2.4870875104071035</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <v>14.174001243299999</v>
       </c>
@@ -5831,7 +5751,7 @@
         <v>2.4870875118820934</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>14.174001243299999</v>
       </c>
@@ -5863,7 +5783,7 @@
         <v>2.4870875127020975</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
         <v>14.174001243299999</v>
       </c>
@@ -5895,7 +5815,7 @@
         <v>2.4870875094622824</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
         <v>14.174001243299999</v>
       </c>
@@ -5927,7 +5847,7 @@
         <v>2.4870875105245225</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
         <v>14.174001243299999</v>
       </c>
@@ -5959,16 +5879,16 @@
         <v>2.4870875106554444</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="L12" s="6"/>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="L13" s="6"/>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="L14" s="6"/>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="L15" s="6"/>
     </row>
   </sheetData>

--- a/Results/Phase 2/Hydrogen/hydrogen climate change breakdown results modified.xlsx
+++ b/Results/Phase 2/Hydrogen/hydrogen climate change breakdown results modified.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11210"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20406"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/abhinabera/Desktop/Prospective-LCA/Results/Phase 2/Hydrogen/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Ongoing projects\Prospective LCA\Results\Phase 2\Hydrogen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4024E4D7-682A-EF4C-A252-C73B108EFF95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0283EBB-A22E-4991-9A74-133E6A87F836}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="14020" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="495" windowWidth="28800" windowHeight="14025" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="hydrogenBAU" sheetId="1" r:id="rId1"/>
@@ -22,19 +22,6 @@
     <sheet name="heat" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -649,9 +636,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Z22"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -728,7 +715,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -808,7 +795,7 @@
         <v>8.925189945964096</v>
       </c>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -888,7 +875,7 @@
         <v>8.9251899470263911</v>
       </c>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -968,7 +955,7 @@
         <v>8.9251899486073523</v>
       </c>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -1048,7 +1035,7 @@
         <v>8.92518995142912</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -1128,7 +1115,7 @@
         <v>8.9251899704523812</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -1208,7 +1195,7 @@
         <v>8.9251899763420965</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -1288,7 +1275,7 @@
         <v>8.9251899778341794</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -1368,7 +1355,7 @@
         <v>8.9251899529845442</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -1448,7 +1435,7 @@
         <v>8.9251899679516775</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -1528,61 +1515,61 @@
         <v>8.9251899774749894</v>
       </c>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
       <c r="D13" s="5">
         <f>($D$2-D3)/$D$2*100</f>
         <v>1.7381816828182749E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
       <c r="D14" s="5">
         <f t="shared" ref="D14:D21" si="0">($D$2-D4)/$D$2*100</f>
         <v>-0.18536699616302277</v>
       </c>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
       <c r="D15" s="5">
         <f t="shared" si="0"/>
         <v>-0.75119689889022923</v>
       </c>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
       <c r="D16" s="5">
         <f t="shared" si="0"/>
         <v>-4.1722557989019737</v>
       </c>
     </row>
-    <row r="17" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D17" s="5">
         <f t="shared" si="0"/>
         <v>-5.0159405042811356</v>
       </c>
     </row>
-    <row r="18" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="18" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D18" s="5">
         <f t="shared" si="0"/>
         <v>-5.1242939129246494</v>
       </c>
     </row>
-    <row r="19" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="5">
         <f t="shared" si="0"/>
         <v>-0.97102431619190166</v>
       </c>
     </row>
-    <row r="20" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="20" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D20" s="5">
         <f t="shared" si="0"/>
         <v>-3.7542312601776713</v>
       </c>
     </row>
-    <row r="21" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="21" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D21" s="5">
         <f t="shared" si="0"/>
         <v>-5.5531358956240853</v>
       </c>
     </row>
-    <row r="22" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="22" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D22" s="5">
         <f>MAX(D13:D21)</f>
         <v>1.7381816828182749E-2</v>
@@ -1596,9 +1583,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AB11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1681,7 +1668,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -1767,7 +1754,7 @@
         <v>2.6131052507600758</v>
       </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -1853,7 +1840,7 @@
         <v>2.6131052514145008</v>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -1939,7 +1926,7 @@
         <v>2.613105251801672</v>
       </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -2025,7 +2012,7 @@
         <v>2.6131052517288169</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -2111,7 +2098,7 @@
         <v>2.61310525145604</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -2197,7 +2184,7 @@
         <v>2.6131052524615779</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -2283,7 +2270,7 @@
         <v>2.6131052531549179</v>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -2369,7 +2356,7 @@
         <v>2.6131052518285678</v>
       </c>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -2455,7 +2442,7 @@
         <v>2.6131052517506932</v>
       </c>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -2549,9 +2536,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:AA22"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2631,7 +2618,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -2714,7 +2701,7 @@
         <v>7.6640674917755538</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -2797,7 +2784,7 @@
         <v>7.6640674915452065</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -2880,7 +2867,7 @@
         <v>7.6640674914023341</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -2963,7 +2950,7 @@
         <v>7.6640674913841584</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -3046,7 +3033,7 @@
         <v>7.6640674907678461</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -3129,7 +3116,7 @@
         <v>7.664067490274161</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -3212,7 +3199,7 @@
         <v>7.6640674900439452</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -3295,7 +3282,7 @@
         <v>7.6640674912127844</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -3378,7 +3365,7 @@
         <v>7.6640674906770707</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -3461,34 +3448,34 @@
         <v>7.6640674906283612</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="D13" s="5"/>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="D14" s="5"/>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="D15" s="5"/>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
       <c r="D16" s="5"/>
     </row>
-    <row r="17" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D17" s="5"/>
     </row>
-    <row r="18" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="18" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D18" s="5"/>
     </row>
-    <row r="19" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="5"/>
     </row>
-    <row r="20" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="20" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D20" s="5"/>
     </row>
-    <row r="21" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="21" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D21" s="5"/>
     </row>
-    <row r="22" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="22" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D22" s="9"/>
     </row>
   </sheetData>
@@ -3499,9 +3486,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:AC11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3587,7 +3574,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -3676,7 +3663,7 @@
         <v>2.4870875078361037</v>
       </c>
     </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -3765,7 +3752,7 @@
         <v>2.4870875085855886</v>
       </c>
     </row>
-    <row r="4" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -3854,7 +3841,7 @@
         <v>2.4870875090995366</v>
       </c>
     </row>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -3943,7 +3930,7 @@
         <v>2.4870875092355385</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -4032,7 +4019,7 @@
         <v>2.4870875104071035</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -4121,7 +4108,7 @@
         <v>2.4870875118820934</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -4210,7 +4197,7 @@
         <v>2.4870875127020975</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -4299,7 +4286,7 @@
         <v>2.4870875094622824</v>
       </c>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -4388,7 +4375,7 @@
         <v>2.4870875105245225</v>
       </c>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -4485,9 +4472,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:M22"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4525,7 +4512,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -4566,7 +4553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -4607,7 +4594,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -4648,7 +4635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -4689,7 +4676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -4730,7 +4717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -4771,7 +4758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -4812,7 +4799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -4853,7 +4840,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -4894,7 +4881,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -4935,34 +4922,34 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="D13" s="5"/>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="D14" s="5"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="D15" s="5"/>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="D16" s="5"/>
     </row>
-    <row r="17" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D17" s="5"/>
     </row>
-    <row r="18" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="18" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D18" s="5"/>
     </row>
-    <row r="19" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="5"/>
     </row>
-    <row r="20" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="20" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D20" s="5"/>
     </row>
-    <row r="21" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="21" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D21" s="5"/>
     </row>
-    <row r="22" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="22" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D22" s="9"/>
     </row>
   </sheetData>
@@ -4973,9 +4960,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:M22"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5013,7 +5000,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -5054,7 +5041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -5095,7 +5082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -5136,7 +5123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -5177,7 +5164,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -5218,7 +5205,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -5259,7 +5246,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -5300,7 +5287,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -5341,7 +5328,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -5382,7 +5369,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -5423,34 +5410,34 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="D13" s="5"/>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="D14" s="5"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="D15" s="5"/>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="D16" s="5"/>
     </row>
-    <row r="17" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D17" s="5"/>
     </row>
-    <row r="18" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="18" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D18" s="5"/>
     </row>
-    <row r="19" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="5"/>
     </row>
-    <row r="20" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="20" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D20" s="5"/>
     </row>
-    <row r="21" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="21" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D21" s="5"/>
     </row>
-    <row r="22" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="22" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D22" s="9"/>
     </row>
   </sheetData>
@@ -5461,24 +5448,24 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8AD273D-583A-4357-8767-B2CE3C4BA43A}">
   <dimension ref="A1:O15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.83203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.42578125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.83203125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="24.5" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.83203125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="24.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="24.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>42</v>
       </c>
@@ -5519,7 +5506,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>14.174001243299999</v>
       </c>
@@ -5560,7 +5547,7 @@
         <v>2.4870875078361037</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>14.174001243299999</v>
       </c>
@@ -5603,7 +5590,7 @@
         <v>2.4870875085855886</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>14.174001243299999</v>
       </c>
@@ -5644,7 +5631,7 @@
         <v>2.4870875090995366</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>14.174001243299999</v>
       </c>
@@ -5687,7 +5674,7 @@
         <v>2.4870875092355385</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>14.174001243299999</v>
       </c>
@@ -5719,7 +5706,7 @@
         <v>2.4870875104071035</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>14.174001243299999</v>
       </c>
@@ -5751,7 +5738,7 @@
         <v>2.4870875118820934</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>14.174001243299999</v>
       </c>
@@ -5783,7 +5770,7 @@
         <v>2.4870875127020975</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>14.174001243299999</v>
       </c>
@@ -5815,7 +5802,7 @@
         <v>2.4870875094622824</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>14.174001243299999</v>
       </c>
@@ -5847,7 +5834,7 @@
         <v>2.4870875105245225</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>14.174001243299999</v>
       </c>
@@ -5879,16 +5866,16 @@
         <v>2.4870875106554444</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="L12" s="6"/>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="L13" s="6"/>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="L14" s="6"/>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="L15" s="6"/>
     </row>
   </sheetData>
